--- a/diseases/d023/2005-2009.xlsx
+++ b/diseases/d023/2005-2009.xlsx
@@ -913,9 +913,6 @@
       <c r="O3" t="n">
         <v>0</v>
       </c>
-      <c r="Q3" t="n">
-        <v>0</v>
-      </c>
       <c r="R3" t="n">
         <v>0</v>
       </c>
@@ -1309,9 +1306,6 @@
       <c r="O5" t="n">
         <v>0</v>
       </c>
-      <c r="Q5" t="n">
-        <v>0</v>
-      </c>
       <c r="R5" t="n">
         <v>0</v>
       </c>
@@ -1605,9 +1599,6 @@
       <c r="O7" t="n">
         <v>0</v>
       </c>
-      <c r="Q7" t="n">
-        <v>0</v>
-      </c>
       <c r="R7" t="n">
         <v>0</v>
       </c>
@@ -1901,9 +1892,6 @@
       <c r="O9" t="n">
         <v>0</v>
       </c>
-      <c r="Q9" t="n">
-        <v>0</v>
-      </c>
       <c r="R9" t="n">
         <v>0</v>
       </c>
@@ -2197,9 +2185,6 @@
       <c r="O11" t="n">
         <v>0</v>
       </c>
-      <c r="Q11" t="n">
-        <v>0</v>
-      </c>
       <c r="R11" t="n">
         <v>0</v>
       </c>
@@ -2493,9 +2478,6 @@
       <c r="O13" t="n">
         <v>0</v>
       </c>
-      <c r="Q13" t="n">
-        <v>0</v>
-      </c>
       <c r="R13" t="n">
         <v>0</v>
       </c>
@@ -2789,9 +2771,6 @@
       <c r="O15" t="n">
         <v>0</v>
       </c>
-      <c r="Q15" t="n">
-        <v>0</v>
-      </c>
       <c r="R15" t="n">
         <v>0</v>
       </c>
@@ -3085,9 +3064,6 @@
       <c r="O17" t="n">
         <v>0</v>
       </c>
-      <c r="Q17" t="n">
-        <v>0</v>
-      </c>
       <c r="R17" t="n">
         <v>0</v>
       </c>
@@ -3381,9 +3357,6 @@
       <c r="O19" t="n">
         <v>0</v>
       </c>
-      <c r="Q19" t="n">
-        <v>0</v>
-      </c>
       <c r="R19" t="n">
         <v>0</v>
       </c>
@@ -3677,9 +3650,6 @@
       <c r="O21" t="n">
         <v>0</v>
       </c>
-      <c r="Q21" t="n">
-        <v>0</v>
-      </c>
       <c r="R21" t="n">
         <v>0</v>
       </c>
@@ -3973,9 +3943,6 @@
       <c r="O23" t="n">
         <v>0</v>
       </c>
-      <c r="Q23" t="n">
-        <v>0</v>
-      </c>
       <c r="R23" t="n">
         <v>0</v>
       </c>
@@ -4269,9 +4236,6 @@
       <c r="O25" t="n">
         <v>0</v>
       </c>
-      <c r="Q25" t="n">
-        <v>0</v>
-      </c>
       <c r="R25" t="n">
         <v>0</v>
       </c>
@@ -4565,9 +4529,6 @@
       <c r="O27" t="n">
         <v>0</v>
       </c>
-      <c r="Q27" t="n">
-        <v>0</v>
-      </c>
       <c r="R27" t="n">
         <v>0</v>
       </c>
@@ -4861,9 +4822,6 @@
       <c r="O29" t="n">
         <v>0</v>
       </c>
-      <c r="Q29" t="n">
-        <v>0</v>
-      </c>
       <c r="R29" t="n">
         <v>0</v>
       </c>
@@ -5257,9 +5215,6 @@
       <c r="O31" t="n">
         <v>0</v>
       </c>
-      <c r="Q31" t="n">
-        <v>0</v>
-      </c>
       <c r="R31" t="n">
         <v>0</v>
       </c>
@@ -5553,9 +5508,6 @@
       <c r="O33" t="n">
         <v>0</v>
       </c>
-      <c r="Q33" t="n">
-        <v>0</v>
-      </c>
       <c r="R33" t="n">
         <v>0</v>
       </c>
@@ -5849,9 +5801,6 @@
       <c r="O35" t="n">
         <v>0</v>
       </c>
-      <c r="Q35" t="n">
-        <v>0</v>
-      </c>
       <c r="R35" t="n">
         <v>0</v>
       </c>
@@ -6145,9 +6094,6 @@
       <c r="O37" t="n">
         <v>0</v>
       </c>
-      <c r="Q37" t="n">
-        <v>0</v>
-      </c>
       <c r="R37" t="n">
         <v>0</v>
       </c>
@@ -6441,9 +6387,6 @@
       <c r="O39" t="n">
         <v>0</v>
       </c>
-      <c r="Q39" t="n">
-        <v>0</v>
-      </c>
       <c r="R39" t="n">
         <v>0</v>
       </c>
@@ -6737,9 +6680,6 @@
       <c r="O41" t="n">
         <v>0</v>
       </c>
-      <c r="Q41" t="n">
-        <v>0</v>
-      </c>
       <c r="R41" t="n">
         <v>0</v>
       </c>
@@ -7033,9 +6973,6 @@
       <c r="O43" t="n">
         <v>0</v>
       </c>
-      <c r="Q43" t="n">
-        <v>0</v>
-      </c>
       <c r="R43" t="n">
         <v>0</v>
       </c>
@@ -7329,9 +7266,6 @@
       <c r="O45" t="n">
         <v>0</v>
       </c>
-      <c r="Q45" t="n">
-        <v>0</v>
-      </c>
       <c r="R45" t="n">
         <v>0</v>
       </c>
@@ -7625,9 +7559,6 @@
       <c r="O47" t="n">
         <v>0</v>
       </c>
-      <c r="Q47" t="n">
-        <v>0</v>
-      </c>
       <c r="R47" t="n">
         <v>0</v>
       </c>
@@ -7921,9 +7852,6 @@
       <c r="O49" t="n">
         <v>0</v>
       </c>
-      <c r="Q49" t="n">
-        <v>0</v>
-      </c>
       <c r="R49" t="n">
         <v>0</v>
       </c>
@@ -8217,9 +8145,6 @@
       <c r="O51" t="n">
         <v>0</v>
       </c>
-      <c r="Q51" t="n">
-        <v>0</v>
-      </c>
       <c r="R51" t="n">
         <v>0</v>
       </c>
@@ -8513,9 +8438,6 @@
       <c r="O53" t="n">
         <v>0</v>
       </c>
-      <c r="Q53" t="n">
-        <v>0</v>
-      </c>
       <c r="R53" t="n">
         <v>0</v>
       </c>
@@ -8809,9 +8731,6 @@
       <c r="O55" t="n">
         <v>0</v>
       </c>
-      <c r="Q55" t="n">
-        <v>0</v>
-      </c>
       <c r="R55" t="n">
         <v>0</v>
       </c>
@@ -9205,9 +9124,6 @@
       <c r="O57" t="n">
         <v>0</v>
       </c>
-      <c r="Q57" t="n">
-        <v>0</v>
-      </c>
       <c r="R57" t="n">
         <v>0</v>
       </c>
@@ -9501,9 +9417,6 @@
       <c r="O59" t="n">
         <v>0</v>
       </c>
-      <c r="Q59" t="n">
-        <v>0</v>
-      </c>
       <c r="R59" t="n">
         <v>0</v>
       </c>
@@ -9797,9 +9710,6 @@
       <c r="O61" t="n">
         <v>0</v>
       </c>
-      <c r="Q61" t="n">
-        <v>0</v>
-      </c>
       <c r="R61" t="n">
         <v>0</v>
       </c>
@@ -10093,9 +10003,6 @@
       <c r="O63" t="n">
         <v>0</v>
       </c>
-      <c r="Q63" t="n">
-        <v>0</v>
-      </c>
       <c r="R63" t="n">
         <v>0</v>
       </c>
@@ -10389,9 +10296,6 @@
       <c r="O65" t="n">
         <v>0</v>
       </c>
-      <c r="Q65" t="n">
-        <v>0</v>
-      </c>
       <c r="R65" t="n">
         <v>0</v>
       </c>
@@ -10685,9 +10589,6 @@
       <c r="O67" t="n">
         <v>0</v>
       </c>
-      <c r="Q67" t="n">
-        <v>0</v>
-      </c>
       <c r="R67" t="n">
         <v>0</v>
       </c>
@@ -10981,9 +10882,6 @@
       <c r="O69" t="n">
         <v>0</v>
       </c>
-      <c r="Q69" t="n">
-        <v>0</v>
-      </c>
       <c r="R69" t="n">
         <v>0</v>
       </c>
@@ -11277,9 +11175,6 @@
       <c r="O71" t="n">
         <v>0</v>
       </c>
-      <c r="Q71" t="n">
-        <v>0</v>
-      </c>
       <c r="R71" t="n">
         <v>0</v>
       </c>
@@ -11573,9 +11468,6 @@
       <c r="O73" t="n">
         <v>0</v>
       </c>
-      <c r="Q73" t="n">
-        <v>0</v>
-      </c>
       <c r="R73" t="n">
         <v>0</v>
       </c>
@@ -11869,9 +11761,6 @@
       <c r="O75" t="n">
         <v>0</v>
       </c>
-      <c r="Q75" t="n">
-        <v>0</v>
-      </c>
       <c r="R75" t="n">
         <v>0</v>
       </c>
@@ -12165,9 +12054,6 @@
       <c r="O77" t="n">
         <v>0</v>
       </c>
-      <c r="Q77" t="n">
-        <v>0</v>
-      </c>
       <c r="R77" t="n">
         <v>0</v>
       </c>
@@ -12461,9 +12347,6 @@
       <c r="O79" t="n">
         <v>0</v>
       </c>
-      <c r="Q79" t="n">
-        <v>0</v>
-      </c>
       <c r="R79" t="n">
         <v>0</v>
       </c>
@@ -12757,9 +12640,6 @@
       <c r="O81" t="n">
         <v>0</v>
       </c>
-      <c r="Q81" t="n">
-        <v>0</v>
-      </c>
       <c r="R81" t="n">
         <v>0</v>
       </c>
@@ -13153,9 +13033,6 @@
       <c r="O83" t="n">
         <v>0</v>
       </c>
-      <c r="Q83" t="n">
-        <v>0</v>
-      </c>
       <c r="R83" t="n">
         <v>0</v>
       </c>
@@ -13449,9 +13326,6 @@
       <c r="O85" t="n">
         <v>0</v>
       </c>
-      <c r="Q85" t="n">
-        <v>0</v>
-      </c>
       <c r="R85" t="n">
         <v>0</v>
       </c>
@@ -13745,9 +13619,6 @@
       <c r="O87" t="n">
         <v>0</v>
       </c>
-      <c r="Q87" t="n">
-        <v>0</v>
-      </c>
       <c r="R87" t="n">
         <v>0</v>
       </c>
@@ -14041,9 +13912,6 @@
       <c r="O89" t="n">
         <v>0</v>
       </c>
-      <c r="Q89" t="n">
-        <v>0</v>
-      </c>
       <c r="R89" t="n">
         <v>0</v>
       </c>
@@ -14337,9 +14205,6 @@
       <c r="O91" t="n">
         <v>0</v>
       </c>
-      <c r="Q91" t="n">
-        <v>0</v>
-      </c>
       <c r="R91" t="n">
         <v>0</v>
       </c>
@@ -14633,9 +14498,6 @@
       <c r="O93" t="n">
         <v>0</v>
       </c>
-      <c r="Q93" t="n">
-        <v>0</v>
-      </c>
       <c r="R93" t="n">
         <v>0</v>
       </c>
@@ -15077,9 +14939,6 @@
       <c r="O96" t="n">
         <v>0</v>
       </c>
-      <c r="Q96" t="n">
-        <v>0</v>
-      </c>
       <c r="R96" t="n">
         <v>0</v>
       </c>
@@ -15521,9 +15380,6 @@
       <c r="O99" t="n">
         <v>0</v>
       </c>
-      <c r="Q99" t="n">
-        <v>0</v>
-      </c>
       <c r="R99" t="n">
         <v>0</v>
       </c>
@@ -15965,9 +15821,6 @@
       <c r="O102" t="n">
         <v>0</v>
       </c>
-      <c r="Q102" t="n">
-        <v>0</v>
-      </c>
       <c r="R102" t="n">
         <v>0</v>
       </c>
@@ -16409,9 +16262,6 @@
       <c r="O105" t="n">
         <v>0</v>
       </c>
-      <c r="Q105" t="n">
-        <v>0</v>
-      </c>
       <c r="R105" t="n">
         <v>0</v>
       </c>
@@ -16853,9 +16703,6 @@
       <c r="O108" t="n">
         <v>0</v>
       </c>
-      <c r="Q108" t="n">
-        <v>0</v>
-      </c>
       <c r="R108" t="n">
         <v>0</v>
       </c>
@@ -17297,9 +17144,6 @@
       <c r="O111" t="n">
         <v>0</v>
       </c>
-      <c r="Q111" t="n">
-        <v>0</v>
-      </c>
       <c r="R111" t="n">
         <v>0</v>
       </c>
@@ -17741,9 +17585,6 @@
       <c r="O114" t="n">
         <v>0</v>
       </c>
-      <c r="Q114" t="n">
-        <v>0</v>
-      </c>
       <c r="R114" t="n">
         <v>0</v>
       </c>
@@ -18137,9 +17978,6 @@
       <c r="O116" t="n">
         <v>0</v>
       </c>
-      <c r="Q116" t="n">
-        <v>0</v>
-      </c>
       <c r="R116" t="n">
         <v>0</v>
       </c>
@@ -18581,9 +18419,6 @@
       <c r="O119" t="n">
         <v>0</v>
       </c>
-      <c r="Q119" t="n">
-        <v>0</v>
-      </c>
       <c r="R119" t="n">
         <v>0</v>
       </c>
@@ -19025,9 +18860,6 @@
       <c r="O122" t="n">
         <v>0</v>
       </c>
-      <c r="Q122" t="n">
-        <v>0</v>
-      </c>
       <c r="R122" t="n">
         <v>0</v>
       </c>
@@ -19469,9 +19301,6 @@
       <c r="O125" t="n">
         <v>0</v>
       </c>
-      <c r="Q125" t="n">
-        <v>0</v>
-      </c>
       <c r="R125" t="n">
         <v>0</v>
       </c>
@@ -19913,9 +19742,6 @@
       <c r="O128" t="n">
         <v>0</v>
       </c>
-      <c r="Q128" t="n">
-        <v>0</v>
-      </c>
       <c r="R128" t="n">
         <v>0</v>
       </c>
@@ -20357,9 +20183,6 @@
       <c r="O131" t="n">
         <v>0</v>
       </c>
-      <c r="Q131" t="n">
-        <v>0</v>
-      </c>
       <c r="R131" t="n">
         <v>0</v>
       </c>
@@ -20801,9 +20624,6 @@
       <c r="O134" t="n">
         <v>0</v>
       </c>
-      <c r="Q134" t="n">
-        <v>0</v>
-      </c>
       <c r="R134" t="n">
         <v>0</v>
       </c>
@@ -21245,9 +21065,6 @@
       <c r="O137" t="n">
         <v>0</v>
       </c>
-      <c r="Q137" t="n">
-        <v>0</v>
-      </c>
       <c r="R137" t="n">
         <v>0</v>
       </c>
@@ -21689,9 +21506,6 @@
       <c r="O140" t="n">
         <v>0</v>
       </c>
-      <c r="Q140" t="n">
-        <v>0</v>
-      </c>
       <c r="R140" t="n">
         <v>0</v>
       </c>
@@ -22133,9 +21947,6 @@
       <c r="O143" t="n">
         <v>0</v>
       </c>
-      <c r="Q143" t="n">
-        <v>0</v>
-      </c>
       <c r="R143" t="n">
         <v>0</v>
       </c>
@@ -22577,9 +22388,6 @@
       <c r="O146" t="n">
         <v>0</v>
       </c>
-      <c r="Q146" t="n">
-        <v>0</v>
-      </c>
       <c r="R146" t="n">
         <v>0</v>
       </c>
@@ -23019,9 +22827,6 @@
         <v>0</v>
       </c>
       <c r="O149" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q149" t="n">
         <v>0</v>
       </c>
       <c r="R149" t="n">

--- a/diseases/d023/2005-2009.xlsx
+++ b/diseases/d023/2005-2009.xlsx
@@ -8687,12 +8687,12 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>IS</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Iceland</t>
+          <t>France</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -8741,7 +8741,7 @@
       </c>
       <c r="U55" t="inlineStr">
         <is>
-          <t>SER_IS_HISTORY_ANTHRAX_ANNUAL</t>
+          <t>SER_FR_ECDC_ANTH_ANNUAL</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -8766,7 +8766,7 @@
       </c>
       <c r="AS55" t="inlineStr">
         <is>
-          <t>SER_IS_HISTORY_ANTHRAX_ANNUAL</t>
+          <t>SER_FR_ECDC_ANTH_ANNUAL</t>
         </is>
       </c>
       <c r="AT55" t="n">
@@ -8779,42 +8779,42 @@
       </c>
       <c r="AV55" t="inlineStr">
         <is>
-          <t>is_doh_annual</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Iceland Directorate of Health Annual Dashboard</t>
+          <t>ECDC Surveillance Atlas — France Annual Baseline</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>https://island.is/en/smitsjukdomar-tolur</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
       <c r="AZ55" t="inlineStr">
         <is>
-          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="BA55" t="inlineStr">
         <is>
-          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
+          <t>ECDC Surveillance Atlas — France Annual Baseline</t>
         </is>
       </c>
       <c r="BB55" t="inlineStr">
         <is>
-          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="BC55" t="inlineStr">
         <is>
-          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
     </row>
@@ -8846,12 +8846,12 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>IS</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Iceland</t>
+          <t>France</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -8892,22 +8892,22 @@
       </c>
       <c r="U56" t="inlineStr">
         <is>
-          <t>SER_IS_HISTORY_ANTHRAX_ANNUAL</t>
+          <t>SER_FR_ECDC_ANTH_ANNUAL</t>
         </is>
       </c>
       <c r="V56" t="inlineStr">
         <is>
-          <t>SER_IS_HISTORY_ANTHRAX_ANNUAL</t>
+          <t>SER_FR_ECDC_ANTH_ANNUAL</t>
         </is>
       </c>
       <c r="W56" t="inlineStr">
         <is>
-          <t>SRC_IS_DOH_HISTORY</t>
+          <t>SRC_FR_ECDC_ATLAS</t>
         </is>
       </c>
       <c r="X56" t="inlineStr">
         <is>
-          <t>Miltisbrandur</t>
+          <t>Anthrax</t>
         </is>
       </c>
       <c r="Y56" t="inlineStr">
@@ -8917,7 +8917,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>national_registry_notifications</t>
+          <t>ecdc_member_state_reported_aggregate_surveillance</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -8932,7 +8932,7 @@
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>country:IS:national</t>
+          <t>country:FR:national</t>
         </is>
       </c>
       <c r="AD56" t="inlineStr">
@@ -8957,7 +8957,7 @@
       </c>
       <c r="AH56" t="inlineStr">
         <is>
-          <t>historical</t>
+          <t>active</t>
         </is>
       </c>
       <c r="AI56" t="inlineStr">
@@ -8967,12 +8967,12 @@
       </c>
       <c r="AJ56" t="inlineStr">
         <is>
-          <t>IS_DOH_historical_registry_annual</t>
+          <t>ECDC_CURRENT_GENERAL_ANNUAL_2026_08</t>
         </is>
       </c>
       <c r="AK56" t="inlineStr">
         <is>
-          <t>Iceland historical national-registry annual notifications; published dashes mean not applicable and blank cells remain unknown.</t>
+          <t>France annual Member-State reported aggregate cases from the public ECDC Surveillance Atlas; published zeroes are explicit, absent topic/year cells remain unknown, and combined populations are emitted only when every reviewed component is present. Data provided by ECDC based on data reported by EU/EEA Member States.</t>
         </is>
       </c>
       <c r="AM56" t="inlineStr">
@@ -9000,7 +9000,7 @@
       </c>
       <c r="AS56" t="inlineStr">
         <is>
-          <t>SER_IS_HISTORY_ANTHRAX_ANNUAL</t>
+          <t>SER_FR_ECDC_ANTH_ANNUAL</t>
         </is>
       </c>
       <c r="AT56" t="n">
@@ -9013,42 +9013,42 @@
       </c>
       <c r="AV56" t="inlineStr">
         <is>
-          <t>is_doh_annual</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Iceland Directorate of Health Annual Dashboard</t>
+          <t>ECDC Surveillance Atlas — France Annual Baseline</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>https://island.is/en/smitsjukdomar-tolur</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
       <c r="AZ56" t="inlineStr">
         <is>
-          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="BA56" t="inlineStr">
         <is>
-          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
+          <t>ECDC Surveillance Atlas — France Annual Baseline</t>
         </is>
       </c>
       <c r="BB56" t="inlineStr">
         <is>
-          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="BC56" t="inlineStr">
         <is>
-          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
     </row>
@@ -9080,12 +9080,12 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>IS</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Iceland</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -9132,68 +9132,82 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>SER_IS_HISTORY_ANTHRAX_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
       <c r="AO57" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP57" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR57" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS57" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ57" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS57" t="inlineStr">
+        <is>
+          <t>SER_IS_HISTORY_ANTHRAX_ANNUAL</t>
+        </is>
+      </c>
       <c r="AT57" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU57" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV57" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>is_doh_annual</t>
         </is>
       </c>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Iceland Directorate of Health Annual Dashboard</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://island.is/en/smitsjukdomar-tolur</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ57" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
         </is>
       </c>
       <c r="BA57" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
         </is>
       </c>
       <c r="BB57" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
         </is>
       </c>
       <c r="BC57" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
         </is>
       </c>
     </row>
@@ -9220,17 +9234,17 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>IS</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Iceland</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -9255,12 +9269,12 @@
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>2007-02-01</t>
+          <t>2007-01-01</t>
         </is>
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>2007-02</t>
+          <t>2007-01</t>
         </is>
       </c>
       <c r="N58" t="n">
@@ -9269,54 +9283,140 @@
       <c r="O58" t="n">
         <v>0</v>
       </c>
-      <c r="Q58" t="n">
-        <v>0</v>
-      </c>
-      <c r="R58" t="n">
-        <v>0</v>
-      </c>
-      <c r="S58" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>SER_IS_HISTORY_ANTHRAX_ANNUAL</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>SER_IS_HISTORY_ANTHRAX_ANNUAL</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>SRC_IS_DOH_HISTORY</t>
+        </is>
+      </c>
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>Miltisbrandur</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z58" t="inlineStr">
+        <is>
+          <t>national_registry_notifications</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="AB58" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>country:IS:national</t>
+        </is>
+      </c>
+      <c r="AD58" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE58" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF58" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG58" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH58" t="inlineStr">
+        <is>
+          <t>historical</t>
+        </is>
+      </c>
+      <c r="AI58" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ58" t="inlineStr">
+        <is>
+          <t>IS_DOH_historical_registry_annual</t>
+        </is>
+      </c>
+      <c r="AK58" t="inlineStr">
+        <is>
+          <t>Iceland historical national-registry annual notifications; published dashes mean not applicable and blank cells remain unknown.</t>
+        </is>
+      </c>
+      <c r="AM58" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN58" t="b">
+        <v>1</v>
       </c>
       <c r="AO58" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP58" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR58" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS58" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ58" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS58" t="inlineStr">
+        <is>
+          <t>SER_IS_HISTORY_ANTHRAX_ANNUAL</t>
+        </is>
+      </c>
       <c r="AT58" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU58" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV58" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>is_doh_annual</t>
         </is>
       </c>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Iceland Directorate of Health Annual Dashboard</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://island.is/en/smitsjukdomar-tolur</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr">
@@ -9326,22 +9426,22 @@
       </c>
       <c r="AZ58" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
         </is>
       </c>
       <c r="BA58" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
         </is>
       </c>
       <c r="BB58" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
         </is>
       </c>
       <c r="BC58" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
         </is>
       </c>
     </row>
@@ -9403,12 +9503,12 @@
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>2007-02-01</t>
+          <t>2007-01-01</t>
         </is>
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>2007-02</t>
+          <t>2007-01</t>
         </is>
       </c>
       <c r="N59" t="n">
@@ -9548,12 +9648,12 @@
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>2007-03-01</t>
+          <t>2007-02-01</t>
         </is>
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>2007-03</t>
+          <t>2007-02</t>
         </is>
       </c>
       <c r="N60" t="n">
@@ -9696,12 +9796,12 @@
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>2007-03-01</t>
+          <t>2007-02-01</t>
         </is>
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>2007-03</t>
+          <t>2007-02</t>
         </is>
       </c>
       <c r="N61" t="n">
@@ -9841,12 +9941,12 @@
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>2007-04-01</t>
+          <t>2007-03-01</t>
         </is>
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>2007-04</t>
+          <t>2007-03</t>
         </is>
       </c>
       <c r="N62" t="n">
@@ -9989,12 +10089,12 @@
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>2007-04-01</t>
+          <t>2007-03-01</t>
         </is>
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>2007-04</t>
+          <t>2007-03</t>
         </is>
       </c>
       <c r="N63" t="n">
@@ -10134,12 +10234,12 @@
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>2007-05-01</t>
+          <t>2007-04-01</t>
         </is>
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>2007-05</t>
+          <t>2007-04</t>
         </is>
       </c>
       <c r="N64" t="n">
@@ -10282,12 +10382,12 @@
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>2007-05-01</t>
+          <t>2007-04-01</t>
         </is>
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>2007-05</t>
+          <t>2007-04</t>
         </is>
       </c>
       <c r="N65" t="n">
@@ -10427,12 +10527,12 @@
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>2007-06-01</t>
+          <t>2007-05-01</t>
         </is>
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>2007-06</t>
+          <t>2007-05</t>
         </is>
       </c>
       <c r="N66" t="n">
@@ -10575,12 +10675,12 @@
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>2007-06-01</t>
+          <t>2007-05-01</t>
         </is>
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>2007-06</t>
+          <t>2007-05</t>
         </is>
       </c>
       <c r="N67" t="n">
@@ -10720,12 +10820,12 @@
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>2007-07-01</t>
+          <t>2007-06-01</t>
         </is>
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>2007-07</t>
+          <t>2007-06</t>
         </is>
       </c>
       <c r="N68" t="n">
@@ -10868,12 +10968,12 @@
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>2007-07-01</t>
+          <t>2007-06-01</t>
         </is>
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>2007-07</t>
+          <t>2007-06</t>
         </is>
       </c>
       <c r="N69" t="n">
@@ -11013,12 +11113,12 @@
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>2007-08-01</t>
+          <t>2007-07-01</t>
         </is>
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t>2007-08</t>
+          <t>2007-07</t>
         </is>
       </c>
       <c r="N70" t="n">
@@ -11161,12 +11261,12 @@
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>2007-08-01</t>
+          <t>2007-07-01</t>
         </is>
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t>2007-08</t>
+          <t>2007-07</t>
         </is>
       </c>
       <c r="N71" t="n">
@@ -11306,12 +11406,12 @@
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>2007-09-01</t>
+          <t>2007-08-01</t>
         </is>
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>2007-09</t>
+          <t>2007-08</t>
         </is>
       </c>
       <c r="N72" t="n">
@@ -11454,12 +11554,12 @@
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>2007-09-01</t>
+          <t>2007-08-01</t>
         </is>
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t>2007-09</t>
+          <t>2007-08</t>
         </is>
       </c>
       <c r="N73" t="n">
@@ -11599,12 +11699,12 @@
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>2007-10-01</t>
+          <t>2007-09-01</t>
         </is>
       </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t>2007-10</t>
+          <t>2007-09</t>
         </is>
       </c>
       <c r="N74" t="n">
@@ -11747,12 +11847,12 @@
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>2007-10-01</t>
+          <t>2007-09-01</t>
         </is>
       </c>
       <c r="M75" t="inlineStr">
         <is>
-          <t>2007-10</t>
+          <t>2007-09</t>
         </is>
       </c>
       <c r="N75" t="n">
@@ -11892,12 +11992,12 @@
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>2007-11-01</t>
+          <t>2007-10-01</t>
         </is>
       </c>
       <c r="M76" t="inlineStr">
         <is>
-          <t>2007-11</t>
+          <t>2007-10</t>
         </is>
       </c>
       <c r="N76" t="n">
@@ -12040,12 +12140,12 @@
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>2007-11-01</t>
+          <t>2007-10-01</t>
         </is>
       </c>
       <c r="M77" t="inlineStr">
         <is>
-          <t>2007-11</t>
+          <t>2007-10</t>
         </is>
       </c>
       <c r="N77" t="n">
@@ -12185,12 +12285,12 @@
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>2007-12-01</t>
+          <t>2007-11-01</t>
         </is>
       </c>
       <c r="M78" t="inlineStr">
         <is>
-          <t>2007-12</t>
+          <t>2007-11</t>
         </is>
       </c>
       <c r="N78" t="n">
@@ -12333,12 +12433,12 @@
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>2007-12-01</t>
+          <t>2007-11-01</t>
         </is>
       </c>
       <c r="M79" t="inlineStr">
         <is>
-          <t>2007-12</t>
+          <t>2007-11</t>
         </is>
       </c>
       <c r="N79" t="n">
@@ -12478,12 +12578,12 @@
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>2008-01-01</t>
+          <t>2007-12-01</t>
         </is>
       </c>
       <c r="M80" t="inlineStr">
         <is>
-          <t>2008-01</t>
+          <t>2007-12</t>
         </is>
       </c>
       <c r="N80" t="n">
@@ -12596,12 +12696,12 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>IS</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Iceland</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -12626,12 +12726,12 @@
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>2008-01-01</t>
+          <t>2007-12-01</t>
         </is>
       </c>
       <c r="M81" t="inlineStr">
         <is>
-          <t>2008-01</t>
+          <t>2007-12</t>
         </is>
       </c>
       <c r="N81" t="n">
@@ -12648,82 +12748,68 @@
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U81" t="inlineStr">
-        <is>
-          <t>SER_IS_HISTORY_ANTHRAX_ANNUAL</t>
-        </is>
-      </c>
-      <c r="AA81" t="inlineStr">
-        <is>
-          <t>annual</t>
-        </is>
-      </c>
       <c r="AO81" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP81" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ81" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS81" t="inlineStr">
-        <is>
-          <t>SER_IS_HISTORY_ANTHRAX_ANNUAL</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR81" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS81" t="inlineStr"/>
       <c r="AT81" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU81" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV81" t="inlineStr">
         <is>
-          <t>is_doh_annual</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Iceland Directorate of Health Annual Dashboard</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>https://island.is/en/smitsjukdomar-tolur</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ81" t="inlineStr">
         <is>
-          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA81" t="inlineStr">
         <is>
-          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB81" t="inlineStr">
         <is>
-          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC81" t="inlineStr">
         <is>
-          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -12750,17 +12836,17 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>IS</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Iceland</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -12799,140 +12885,54 @@
       <c r="O82" t="n">
         <v>0</v>
       </c>
-      <c r="U82" t="inlineStr">
-        <is>
-          <t>SER_IS_HISTORY_ANTHRAX_ANNUAL</t>
-        </is>
-      </c>
-      <c r="V82" t="inlineStr">
-        <is>
-          <t>SER_IS_HISTORY_ANTHRAX_ANNUAL</t>
-        </is>
-      </c>
-      <c r="W82" t="inlineStr">
-        <is>
-          <t>SRC_IS_DOH_HISTORY</t>
-        </is>
-      </c>
-      <c r="X82" t="inlineStr">
-        <is>
-          <t>Miltisbrandur</t>
-        </is>
-      </c>
-      <c r="Y82" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z82" t="inlineStr">
-        <is>
-          <t>national_registry_notifications</t>
-        </is>
-      </c>
-      <c r="AA82" t="inlineStr">
-        <is>
-          <t>annual</t>
-        </is>
-      </c>
-      <c r="AB82" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC82" t="inlineStr">
-        <is>
-          <t>country:IS:national</t>
-        </is>
-      </c>
-      <c r="AD82" t="inlineStr">
+      <c r="Q82" t="n">
+        <v>0</v>
+      </c>
+      <c r="R82" t="n">
+        <v>0</v>
+      </c>
+      <c r="S82" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO82" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP82" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR82" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS82" t="inlineStr"/>
+      <c r="AT82" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU82" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV82" t="inlineStr">
         <is>
           <t>all</t>
         </is>
       </c>
-      <c r="AE82" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF82" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG82" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH82" t="inlineStr">
-        <is>
-          <t>historical</t>
-        </is>
-      </c>
-      <c r="AI82" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ82" t="inlineStr">
-        <is>
-          <t>IS_DOH_historical_registry_annual</t>
-        </is>
-      </c>
-      <c r="AK82" t="inlineStr">
-        <is>
-          <t>Iceland historical national-registry annual notifications; published dashes mean not applicable and blank cells remain unknown.</t>
-        </is>
-      </c>
-      <c r="AM82" t="inlineStr">
-        <is>
-          <t>raw</t>
-        </is>
-      </c>
-      <c r="AN82" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO82" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP82" t="inlineStr">
-        <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ82" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS82" t="inlineStr">
-        <is>
-          <t>SER_IS_HISTORY_ANTHRAX_ANNUAL</t>
-        </is>
-      </c>
-      <c r="AT82" t="n">
-        <v>1</v>
-      </c>
-      <c r="AU82" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series.</t>
-        </is>
-      </c>
-      <c r="AV82" t="inlineStr">
-        <is>
-          <t>is_doh_annual</t>
-        </is>
-      </c>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Iceland Directorate of Health Annual Dashboard</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>https://island.is/en/smitsjukdomar-tolur</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr">
@@ -12942,22 +12942,22 @@
       </c>
       <c r="AZ82" t="inlineStr">
         <is>
-          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA82" t="inlineStr">
         <is>
-          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB82" t="inlineStr">
         <is>
-          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC82" t="inlineStr">
         <is>
-          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -12989,12 +12989,12 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>France</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -13041,68 +13041,82 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U83" t="inlineStr">
+        <is>
+          <t>SER_FR_ECDC_ANTH_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AA83" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
       <c r="AO83" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP83" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR83" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS83" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ83" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS83" t="inlineStr">
+        <is>
+          <t>SER_FR_ECDC_ANTH_ANNUAL</t>
+        </is>
+      </c>
       <c r="AT83" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU83" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV83" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>ECDC Surveillance Atlas — France Annual Baseline</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
       <c r="AZ83" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="BA83" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>ECDC Surveillance Atlas — France Annual Baseline</t>
         </is>
       </c>
       <c r="BB83" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="BC83" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
     </row>
@@ -13129,17 +13143,17 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>France</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -13164,12 +13178,12 @@
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>2008-02-01</t>
+          <t>2008-01-01</t>
         </is>
       </c>
       <c r="M84" t="inlineStr">
         <is>
-          <t>2008-02</t>
+          <t>2008-01</t>
         </is>
       </c>
       <c r="N84" t="n">
@@ -13178,79 +13192,165 @@
       <c r="O84" t="n">
         <v>0</v>
       </c>
-      <c r="Q84" t="n">
-        <v>0</v>
-      </c>
-      <c r="R84" t="n">
-        <v>0</v>
-      </c>
-      <c r="S84" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+      <c r="U84" t="inlineStr">
+        <is>
+          <t>SER_FR_ECDC_ANTH_ANNUAL</t>
+        </is>
+      </c>
+      <c r="V84" t="inlineStr">
+        <is>
+          <t>SER_FR_ECDC_ANTH_ANNUAL</t>
+        </is>
+      </c>
+      <c r="W84" t="inlineStr">
+        <is>
+          <t>SRC_FR_ECDC_ATLAS</t>
+        </is>
+      </c>
+      <c r="X84" t="inlineStr">
+        <is>
+          <t>Anthrax</t>
+        </is>
+      </c>
+      <c r="Y84" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z84" t="inlineStr">
+        <is>
+          <t>ecdc_member_state_reported_aggregate_surveillance</t>
+        </is>
+      </c>
+      <c r="AA84" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="AB84" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC84" t="inlineStr">
+        <is>
+          <t>country:FR:national</t>
+        </is>
+      </c>
+      <c r="AD84" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE84" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF84" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG84" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH84" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI84" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ84" t="inlineStr">
+        <is>
+          <t>ECDC_CURRENT_GENERAL_ANNUAL_2026_08</t>
+        </is>
+      </c>
+      <c r="AK84" t="inlineStr">
+        <is>
+          <t>France annual Member-State reported aggregate cases from the public ECDC Surveillance Atlas; published zeroes are explicit, absent topic/year cells remain unknown, and combined populations are emitted only when every reviewed component is present. Data provided by ECDC based on data reported by EU/EEA Member States.</t>
+        </is>
+      </c>
+      <c r="AM84" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN84" t="b">
+        <v>1</v>
       </c>
       <c r="AO84" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP84" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR84" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS84" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ84" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS84" t="inlineStr">
+        <is>
+          <t>SER_FR_ECDC_ANTH_ANNUAL</t>
+        </is>
+      </c>
       <c r="AT84" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU84" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV84" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>ECDC Surveillance Atlas — France Annual Baseline</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
       <c r="AZ84" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="BA84" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>ECDC Surveillance Atlas — France Annual Baseline</t>
         </is>
       </c>
       <c r="BB84" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="BC84" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
     </row>
@@ -13282,12 +13382,12 @@
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>IS</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Iceland</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -13312,12 +13412,12 @@
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>2008-02-01</t>
+          <t>2008-01-01</t>
         </is>
       </c>
       <c r="M85" t="inlineStr">
         <is>
-          <t>2008-02</t>
+          <t>2008-01</t>
         </is>
       </c>
       <c r="N85" t="n">
@@ -13334,68 +13434,82 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U85" t="inlineStr">
+        <is>
+          <t>SER_IS_HISTORY_ANTHRAX_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AA85" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
       <c r="AO85" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP85" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR85" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS85" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ85" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS85" t="inlineStr">
+        <is>
+          <t>SER_IS_HISTORY_ANTHRAX_ANNUAL</t>
+        </is>
+      </c>
       <c r="AT85" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU85" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV85" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>is_doh_annual</t>
         </is>
       </c>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Iceland Directorate of Health Annual Dashboard</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://island.is/en/smitsjukdomar-tolur</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ85" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
         </is>
       </c>
       <c r="BA85" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
         </is>
       </c>
       <c r="BB85" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
         </is>
       </c>
       <c r="BC85" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
         </is>
       </c>
     </row>
@@ -13422,17 +13536,17 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>IS</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Iceland</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -13457,12 +13571,12 @@
       </c>
       <c r="L86" t="inlineStr">
         <is>
-          <t>2008-03-01</t>
+          <t>2008-01-01</t>
         </is>
       </c>
       <c r="M86" t="inlineStr">
         <is>
-          <t>2008-03</t>
+          <t>2008-01</t>
         </is>
       </c>
       <c r="N86" t="n">
@@ -13471,54 +13585,140 @@
       <c r="O86" t="n">
         <v>0</v>
       </c>
-      <c r="Q86" t="n">
-        <v>0</v>
-      </c>
-      <c r="R86" t="n">
-        <v>0</v>
-      </c>
-      <c r="S86" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+      <c r="U86" t="inlineStr">
+        <is>
+          <t>SER_IS_HISTORY_ANTHRAX_ANNUAL</t>
+        </is>
+      </c>
+      <c r="V86" t="inlineStr">
+        <is>
+          <t>SER_IS_HISTORY_ANTHRAX_ANNUAL</t>
+        </is>
+      </c>
+      <c r="W86" t="inlineStr">
+        <is>
+          <t>SRC_IS_DOH_HISTORY</t>
+        </is>
+      </c>
+      <c r="X86" t="inlineStr">
+        <is>
+          <t>Miltisbrandur</t>
+        </is>
+      </c>
+      <c r="Y86" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z86" t="inlineStr">
+        <is>
+          <t>national_registry_notifications</t>
+        </is>
+      </c>
+      <c r="AA86" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="AB86" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC86" t="inlineStr">
+        <is>
+          <t>country:IS:national</t>
+        </is>
+      </c>
+      <c r="AD86" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE86" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF86" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG86" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH86" t="inlineStr">
+        <is>
+          <t>historical</t>
+        </is>
+      </c>
+      <c r="AI86" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ86" t="inlineStr">
+        <is>
+          <t>IS_DOH_historical_registry_annual</t>
+        </is>
+      </c>
+      <c r="AK86" t="inlineStr">
+        <is>
+          <t>Iceland historical national-registry annual notifications; published dashes mean not applicable and blank cells remain unknown.</t>
+        </is>
+      </c>
+      <c r="AM86" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN86" t="b">
+        <v>1</v>
       </c>
       <c r="AO86" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP86" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR86" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS86" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ86" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS86" t="inlineStr">
+        <is>
+          <t>SER_IS_HISTORY_ANTHRAX_ANNUAL</t>
+        </is>
+      </c>
       <c r="AT86" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU86" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV86" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>is_doh_annual</t>
         </is>
       </c>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Iceland Directorate of Health Annual Dashboard</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://island.is/en/smitsjukdomar-tolur</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr">
@@ -13528,22 +13728,22 @@
       </c>
       <c r="AZ86" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
         </is>
       </c>
       <c r="BA86" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
         </is>
       </c>
       <c r="BB86" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
         </is>
       </c>
       <c r="BC86" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
         </is>
       </c>
     </row>
@@ -13605,12 +13805,12 @@
       </c>
       <c r="L87" t="inlineStr">
         <is>
-          <t>2008-03-01</t>
+          <t>2008-01-01</t>
         </is>
       </c>
       <c r="M87" t="inlineStr">
         <is>
-          <t>2008-03</t>
+          <t>2008-01</t>
         </is>
       </c>
       <c r="N87" t="n">
@@ -13750,12 +13950,12 @@
       </c>
       <c r="L88" t="inlineStr">
         <is>
-          <t>2008-04-01</t>
+          <t>2008-02-01</t>
         </is>
       </c>
       <c r="M88" t="inlineStr">
         <is>
-          <t>2008-04</t>
+          <t>2008-02</t>
         </is>
       </c>
       <c r="N88" t="n">
@@ -13898,12 +14098,12 @@
       </c>
       <c r="L89" t="inlineStr">
         <is>
-          <t>2008-04-01</t>
+          <t>2008-02-01</t>
         </is>
       </c>
       <c r="M89" t="inlineStr">
         <is>
-          <t>2008-04</t>
+          <t>2008-02</t>
         </is>
       </c>
       <c r="N89" t="n">
@@ -14043,12 +14243,12 @@
       </c>
       <c r="L90" t="inlineStr">
         <is>
-          <t>2008-05-01</t>
+          <t>2008-03-01</t>
         </is>
       </c>
       <c r="M90" t="inlineStr">
         <is>
-          <t>2008-05</t>
+          <t>2008-03</t>
         </is>
       </c>
       <c r="N90" t="n">
@@ -14191,12 +14391,12 @@
       </c>
       <c r="L91" t="inlineStr">
         <is>
-          <t>2008-05-01</t>
+          <t>2008-03-01</t>
         </is>
       </c>
       <c r="M91" t="inlineStr">
         <is>
-          <t>2008-05</t>
+          <t>2008-03</t>
         </is>
       </c>
       <c r="N91" t="n">
@@ -14336,12 +14536,12 @@
       </c>
       <c r="L92" t="inlineStr">
         <is>
-          <t>2008-06-01</t>
+          <t>2008-04-01</t>
         </is>
       </c>
       <c r="M92" t="inlineStr">
         <is>
-          <t>2008-06</t>
+          <t>2008-04</t>
         </is>
       </c>
       <c r="N92" t="n">
@@ -14484,12 +14684,12 @@
       </c>
       <c r="L93" t="inlineStr">
         <is>
-          <t>2008-06-01</t>
+          <t>2008-04-01</t>
         </is>
       </c>
       <c r="M93" t="inlineStr">
         <is>
-          <t>2008-06</t>
+          <t>2008-04</t>
         </is>
       </c>
       <c r="N93" t="n">
@@ -14629,12 +14829,12 @@
       </c>
       <c r="L94" t="inlineStr">
         <is>
-          <t>2008-07-01</t>
+          <t>2008-05-01</t>
         </is>
       </c>
       <c r="M94" t="inlineStr">
         <is>
-          <t>2008-07</t>
+          <t>2008-05</t>
         </is>
       </c>
       <c r="N94" t="n">
@@ -14747,12 +14947,12 @@
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Hong Kong, China</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
@@ -14777,21 +14977,18 @@
       </c>
       <c r="L95" t="inlineStr">
         <is>
-          <t>2008-07-01</t>
+          <t>2008-05-01</t>
         </is>
       </c>
       <c r="M95" t="inlineStr">
         <is>
-          <t>2008-07</t>
+          <t>2008-05</t>
         </is>
       </c>
       <c r="N95" t="n">
         <v>0</v>
       </c>
       <c r="O95" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q95" t="n">
         <v>0</v>
       </c>
       <c r="R95" t="n">
@@ -14828,42 +15025,42 @@
       </c>
       <c r="AV95" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW95" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ95" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA95" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB95" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC95" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -14895,12 +15092,12 @@
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
@@ -14925,18 +15122,21 @@
       </c>
       <c r="L96" t="inlineStr">
         <is>
-          <t>2008-07-01</t>
+          <t>2008-06-01</t>
         </is>
       </c>
       <c r="M96" t="inlineStr">
         <is>
-          <t>2008-07</t>
+          <t>2008-06</t>
         </is>
       </c>
       <c r="N96" t="n">
         <v>0</v>
       </c>
       <c r="O96" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q96" t="n">
         <v>0</v>
       </c>
       <c r="R96" t="n">
@@ -14973,42 +15173,42 @@
       </c>
       <c r="AV96" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW96" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ96" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA96" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB96" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC96" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -15040,12 +15240,12 @@
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
@@ -15070,21 +15270,18 @@
       </c>
       <c r="L97" t="inlineStr">
         <is>
-          <t>2008-08-01</t>
+          <t>2008-06-01</t>
         </is>
       </c>
       <c r="M97" t="inlineStr">
         <is>
-          <t>2008-08</t>
+          <t>2008-06</t>
         </is>
       </c>
       <c r="N97" t="n">
         <v>0</v>
       </c>
       <c r="O97" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q97" t="n">
         <v>0</v>
       </c>
       <c r="R97" t="n">
@@ -15121,42 +15318,42 @@
       </c>
       <c r="AV97" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW97" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ97" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA97" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB97" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC97" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -15188,12 +15385,12 @@
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Hong Kong, China</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
@@ -15218,12 +15415,12 @@
       </c>
       <c r="L98" t="inlineStr">
         <is>
-          <t>2008-08-01</t>
+          <t>2008-07-01</t>
         </is>
       </c>
       <c r="M98" t="inlineStr">
         <is>
-          <t>2008-08</t>
+          <t>2008-07</t>
         </is>
       </c>
       <c r="N98" t="n">
@@ -15269,42 +15466,42 @@
       </c>
       <c r="AV98" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW98" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ98" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA98" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB98" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC98" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -15336,12 +15533,12 @@
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Hong Kong, China</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
@@ -15366,18 +15563,21 @@
       </c>
       <c r="L99" t="inlineStr">
         <is>
-          <t>2008-08-01</t>
+          <t>2008-07-01</t>
         </is>
       </c>
       <c r="M99" t="inlineStr">
         <is>
-          <t>2008-08</t>
+          <t>2008-07</t>
         </is>
       </c>
       <c r="N99" t="n">
         <v>0</v>
       </c>
       <c r="O99" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q99" t="n">
         <v>0</v>
       </c>
       <c r="R99" t="n">
@@ -15414,42 +15614,42 @@
       </c>
       <c r="AV99" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ99" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="BA99" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB99" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="BC99" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -15481,12 +15681,12 @@
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
@@ -15511,21 +15711,18 @@
       </c>
       <c r="L100" t="inlineStr">
         <is>
-          <t>2008-09-01</t>
+          <t>2008-07-01</t>
         </is>
       </c>
       <c r="M100" t="inlineStr">
         <is>
-          <t>2008-09</t>
+          <t>2008-07</t>
         </is>
       </c>
       <c r="N100" t="n">
         <v>0</v>
       </c>
       <c r="O100" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q100" t="n">
         <v>0</v>
       </c>
       <c r="R100" t="n">
@@ -15562,42 +15759,42 @@
       </c>
       <c r="AV100" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW100" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ100" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA100" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB100" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC100" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -15629,12 +15826,12 @@
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Hong Kong, China</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
@@ -15659,12 +15856,12 @@
       </c>
       <c r="L101" t="inlineStr">
         <is>
-          <t>2008-09-01</t>
+          <t>2008-08-01</t>
         </is>
       </c>
       <c r="M101" t="inlineStr">
         <is>
-          <t>2008-09</t>
+          <t>2008-08</t>
         </is>
       </c>
       <c r="N101" t="n">
@@ -15710,42 +15907,42 @@
       </c>
       <c r="AV101" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW101" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY101" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ101" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA101" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB101" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC101" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -15777,12 +15974,12 @@
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Hong Kong, China</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
@@ -15807,18 +16004,21 @@
       </c>
       <c r="L102" t="inlineStr">
         <is>
-          <t>2008-09-01</t>
+          <t>2008-08-01</t>
         </is>
       </c>
       <c r="M102" t="inlineStr">
         <is>
-          <t>2008-09</t>
+          <t>2008-08</t>
         </is>
       </c>
       <c r="N102" t="n">
         <v>0</v>
       </c>
       <c r="O102" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q102" t="n">
         <v>0</v>
       </c>
       <c r="R102" t="n">
@@ -15855,42 +16055,42 @@
       </c>
       <c r="AV102" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="AW102" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ102" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="BA102" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB102" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="BC102" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -15922,12 +16122,12 @@
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
@@ -15952,21 +16152,18 @@
       </c>
       <c r="L103" t="inlineStr">
         <is>
-          <t>2008-10-01</t>
+          <t>2008-08-01</t>
         </is>
       </c>
       <c r="M103" t="inlineStr">
         <is>
-          <t>2008-10</t>
+          <t>2008-08</t>
         </is>
       </c>
       <c r="N103" t="n">
         <v>0</v>
       </c>
       <c r="O103" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q103" t="n">
         <v>0</v>
       </c>
       <c r="R103" t="n">
@@ -16003,42 +16200,42 @@
       </c>
       <c r="AV103" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW103" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ103" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA103" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB103" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC103" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -16070,12 +16267,12 @@
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Hong Kong, China</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
@@ -16100,12 +16297,12 @@
       </c>
       <c r="L104" t="inlineStr">
         <is>
-          <t>2008-10-01</t>
+          <t>2008-09-01</t>
         </is>
       </c>
       <c r="M104" t="inlineStr">
         <is>
-          <t>2008-10</t>
+          <t>2008-09</t>
         </is>
       </c>
       <c r="N104" t="n">
@@ -16151,42 +16348,42 @@
       </c>
       <c r="AV104" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW104" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ104" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA104" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB104" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC104" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -16218,12 +16415,12 @@
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Hong Kong, China</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
@@ -16248,18 +16445,21 @@
       </c>
       <c r="L105" t="inlineStr">
         <is>
-          <t>2008-10-01</t>
+          <t>2008-09-01</t>
         </is>
       </c>
       <c r="M105" t="inlineStr">
         <is>
-          <t>2008-10</t>
+          <t>2008-09</t>
         </is>
       </c>
       <c r="N105" t="n">
         <v>0</v>
       </c>
       <c r="O105" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q105" t="n">
         <v>0</v>
       </c>
       <c r="R105" t="n">
@@ -16296,42 +16496,42 @@
       </c>
       <c r="AV105" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="AW105" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ105" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="BA105" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB105" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="BC105" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -16363,12 +16563,12 @@
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
@@ -16393,21 +16593,18 @@
       </c>
       <c r="L106" t="inlineStr">
         <is>
-          <t>2008-11-01</t>
+          <t>2008-09-01</t>
         </is>
       </c>
       <c r="M106" t="inlineStr">
         <is>
-          <t>2008-11</t>
+          <t>2008-09</t>
         </is>
       </c>
       <c r="N106" t="n">
         <v>0</v>
       </c>
       <c r="O106" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q106" t="n">
         <v>0</v>
       </c>
       <c r="R106" t="n">
@@ -16444,42 +16641,42 @@
       </c>
       <c r="AV106" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW106" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY106" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ106" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA106" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB106" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC106" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -16511,12 +16708,12 @@
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Hong Kong, China</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
@@ -16541,12 +16738,12 @@
       </c>
       <c r="L107" t="inlineStr">
         <is>
-          <t>2008-11-01</t>
+          <t>2008-10-01</t>
         </is>
       </c>
       <c r="M107" t="inlineStr">
         <is>
-          <t>2008-11</t>
+          <t>2008-10</t>
         </is>
       </c>
       <c r="N107" t="n">
@@ -16592,42 +16789,42 @@
       </c>
       <c r="AV107" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW107" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX107" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY107" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ107" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA107" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB107" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC107" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -16659,12 +16856,12 @@
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Hong Kong, China</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
@@ -16689,18 +16886,21 @@
       </c>
       <c r="L108" t="inlineStr">
         <is>
-          <t>2008-11-01</t>
+          <t>2008-10-01</t>
         </is>
       </c>
       <c r="M108" t="inlineStr">
         <is>
-          <t>2008-11</t>
+          <t>2008-10</t>
         </is>
       </c>
       <c r="N108" t="n">
         <v>0</v>
       </c>
       <c r="O108" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q108" t="n">
         <v>0</v>
       </c>
       <c r="R108" t="n">
@@ -16737,42 +16937,42 @@
       </c>
       <c r="AV108" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="AW108" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX108" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="AY108" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ108" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="BA108" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB108" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="BC108" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -16804,12 +17004,12 @@
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
@@ -16834,21 +17034,18 @@
       </c>
       <c r="L109" t="inlineStr">
         <is>
-          <t>2008-12-01</t>
+          <t>2008-10-01</t>
         </is>
       </c>
       <c r="M109" t="inlineStr">
         <is>
-          <t>2008-12</t>
+          <t>2008-10</t>
         </is>
       </c>
       <c r="N109" t="n">
         <v>0</v>
       </c>
       <c r="O109" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q109" t="n">
         <v>0</v>
       </c>
       <c r="R109" t="n">
@@ -16885,42 +17082,42 @@
       </c>
       <c r="AV109" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW109" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX109" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY109" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ109" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA109" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB109" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC109" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -16952,12 +17149,12 @@
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Hong Kong, China</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
@@ -16982,12 +17179,12 @@
       </c>
       <c r="L110" t="inlineStr">
         <is>
-          <t>2008-12-01</t>
+          <t>2008-11-01</t>
         </is>
       </c>
       <c r="M110" t="inlineStr">
         <is>
-          <t>2008-12</t>
+          <t>2008-11</t>
         </is>
       </c>
       <c r="N110" t="n">
@@ -17033,42 +17230,42 @@
       </c>
       <c r="AV110" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW110" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX110" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY110" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ110" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA110" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB110" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC110" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -17100,12 +17297,12 @@
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Hong Kong, China</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
@@ -17130,18 +17327,21 @@
       </c>
       <c r="L111" t="inlineStr">
         <is>
-          <t>2008-12-01</t>
+          <t>2008-11-01</t>
         </is>
       </c>
       <c r="M111" t="inlineStr">
         <is>
-          <t>2008-12</t>
+          <t>2008-11</t>
         </is>
       </c>
       <c r="N111" t="n">
         <v>0</v>
       </c>
       <c r="O111" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q111" t="n">
         <v>0</v>
       </c>
       <c r="R111" t="n">
@@ -17178,42 +17378,42 @@
       </c>
       <c r="AV111" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="AW111" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX111" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="AY111" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ111" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="BA111" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB111" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="BC111" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -17245,12 +17445,12 @@
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
@@ -17275,21 +17475,18 @@
       </c>
       <c r="L112" t="inlineStr">
         <is>
-          <t>2009-01-01</t>
+          <t>2008-11-01</t>
         </is>
       </c>
       <c r="M112" t="inlineStr">
         <is>
-          <t>2009-01</t>
+          <t>2008-11</t>
         </is>
       </c>
       <c r="N112" t="n">
         <v>0</v>
       </c>
       <c r="O112" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q112" t="n">
         <v>0</v>
       </c>
       <c r="R112" t="n">
@@ -17326,42 +17523,42 @@
       </c>
       <c r="AV112" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW112" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX112" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY112" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ112" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA112" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB112" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC112" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -17393,12 +17590,12 @@
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Hong Kong, China</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
@@ -17423,12 +17620,12 @@
       </c>
       <c r="L113" t="inlineStr">
         <is>
-          <t>2009-01-01</t>
+          <t>2008-12-01</t>
         </is>
       </c>
       <c r="M113" t="inlineStr">
         <is>
-          <t>2009-01</t>
+          <t>2008-12</t>
         </is>
       </c>
       <c r="N113" t="n">
@@ -17474,42 +17671,42 @@
       </c>
       <c r="AV113" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW113" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX113" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY113" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ113" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA113" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB113" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC113" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -17541,12 +17738,12 @@
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>IS</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Iceland</t>
+          <t>Hong Kong, China</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
@@ -17571,12 +17768,12 @@
       </c>
       <c r="L114" t="inlineStr">
         <is>
-          <t>2009-01-01</t>
+          <t>2008-12-01</t>
         </is>
       </c>
       <c r="M114" t="inlineStr">
         <is>
-          <t>2009-01</t>
+          <t>2008-12</t>
         </is>
       </c>
       <c r="N114" t="n">
@@ -17585,6 +17782,9 @@
       <c r="O114" t="n">
         <v>0</v>
       </c>
+      <c r="Q114" t="n">
+        <v>0</v>
+      </c>
       <c r="R114" t="n">
         <v>0</v>
       </c>
@@ -17593,82 +17793,68 @@
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U114" t="inlineStr">
-        <is>
-          <t>SER_IS_HISTORY_ANTHRAX_ANNUAL</t>
-        </is>
-      </c>
-      <c r="AA114" t="inlineStr">
-        <is>
-          <t>annual</t>
-        </is>
-      </c>
       <c r="AO114" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP114" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ114" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS114" t="inlineStr">
-        <is>
-          <t>SER_IS_HISTORY_ANTHRAX_ANNUAL</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR114" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS114" t="inlineStr"/>
       <c r="AT114" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU114" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV114" t="inlineStr">
         <is>
-          <t>is_doh_annual</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="AW114" t="inlineStr">
         <is>
-          <t>Iceland Directorate of Health Annual Dashboard</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX114" t="inlineStr">
         <is>
-          <t>https://island.is/en/smitsjukdomar-tolur</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="AY114" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ114" t="inlineStr">
         <is>
-          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="BA114" t="inlineStr">
         <is>
-          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB114" t="inlineStr">
         <is>
-          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="BC114" t="inlineStr">
         <is>
-          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -17695,17 +17881,17 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>IS</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Iceland</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
@@ -17730,12 +17916,12 @@
       </c>
       <c r="L115" t="inlineStr">
         <is>
-          <t>2009-01-01</t>
+          <t>2008-12-01</t>
         </is>
       </c>
       <c r="M115" t="inlineStr">
         <is>
-          <t>2009-01</t>
+          <t>2008-12</t>
         </is>
       </c>
       <c r="N115" t="n">
@@ -17744,165 +17930,76 @@
       <c r="O115" t="n">
         <v>0</v>
       </c>
-      <c r="U115" t="inlineStr">
-        <is>
-          <t>SER_IS_HISTORY_ANTHRAX_ANNUAL</t>
-        </is>
-      </c>
-      <c r="V115" t="inlineStr">
-        <is>
-          <t>SER_IS_HISTORY_ANTHRAX_ANNUAL</t>
-        </is>
-      </c>
-      <c r="W115" t="inlineStr">
-        <is>
-          <t>SRC_IS_DOH_HISTORY</t>
-        </is>
-      </c>
-      <c r="X115" t="inlineStr">
-        <is>
-          <t>Miltisbrandur</t>
-        </is>
-      </c>
-      <c r="Y115" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z115" t="inlineStr">
-        <is>
-          <t>national_registry_notifications</t>
-        </is>
-      </c>
-      <c r="AA115" t="inlineStr">
-        <is>
-          <t>annual</t>
-        </is>
-      </c>
-      <c r="AB115" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC115" t="inlineStr">
-        <is>
-          <t>country:IS:national</t>
-        </is>
-      </c>
-      <c r="AD115" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE115" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF115" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG115" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH115" t="inlineStr">
-        <is>
-          <t>historical</t>
-        </is>
-      </c>
-      <c r="AI115" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ115" t="inlineStr">
-        <is>
-          <t>IS_DOH_historical_registry_annual</t>
-        </is>
-      </c>
-      <c r="AK115" t="inlineStr">
-        <is>
-          <t>Iceland historical national-registry annual notifications; published dashes mean not applicable and blank cells remain unknown.</t>
-        </is>
-      </c>
-      <c r="AM115" t="inlineStr">
-        <is>
-          <t>raw</t>
-        </is>
-      </c>
-      <c r="AN115" t="b">
-        <v>1</v>
+      <c r="R115" t="n">
+        <v>0</v>
+      </c>
+      <c r="S115" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="AO115" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP115" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ115" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS115" t="inlineStr">
-        <is>
-          <t>SER_IS_HISTORY_ANTHRAX_ANNUAL</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR115" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS115" t="inlineStr"/>
       <c r="AT115" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU115" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV115" t="inlineStr">
         <is>
-          <t>is_doh_annual</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW115" t="inlineStr">
         <is>
-          <t>Iceland Directorate of Health Annual Dashboard</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX115" t="inlineStr">
         <is>
-          <t>https://island.is/en/smitsjukdomar-tolur</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY115" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ115" t="inlineStr">
         <is>
-          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA115" t="inlineStr">
         <is>
-          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB115" t="inlineStr">
         <is>
-          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC115" t="inlineStr">
         <is>
-          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -17934,12 +18031,12 @@
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
@@ -17976,6 +18073,9 @@
         <v>0</v>
       </c>
       <c r="O116" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q116" t="n">
         <v>0</v>
       </c>
       <c r="R116" t="n">
@@ -18012,42 +18112,42 @@
       </c>
       <c r="AV116" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW116" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX116" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY116" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ116" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA116" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB116" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC116" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -18079,12 +18179,12 @@
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>France</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
@@ -18109,12 +18209,12 @@
       </c>
       <c r="L117" t="inlineStr">
         <is>
-          <t>2009-02-01</t>
+          <t>2009-01-01</t>
         </is>
       </c>
       <c r="M117" t="inlineStr">
         <is>
-          <t>2009-02</t>
+          <t>2009-01</t>
         </is>
       </c>
       <c r="N117" t="n">
@@ -18123,9 +18223,6 @@
       <c r="O117" t="n">
         <v>0</v>
       </c>
-      <c r="Q117" t="n">
-        <v>0</v>
-      </c>
       <c r="R117" t="n">
         <v>0</v>
       </c>
@@ -18134,68 +18231,82 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U117" t="inlineStr">
+        <is>
+          <t>SER_FR_ECDC_ANTH_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AA117" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
       <c r="AO117" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP117" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR117" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS117" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ117" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS117" t="inlineStr">
+        <is>
+          <t>SER_FR_ECDC_ANTH_ANNUAL</t>
+        </is>
+      </c>
       <c r="AT117" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU117" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV117" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="AW117" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>ECDC Surveillance Atlas — France Annual Baseline</t>
         </is>
       </c>
       <c r="AX117" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="AY117" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
       <c r="AZ117" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="BA117" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>ECDC Surveillance Atlas — France Annual Baseline</t>
         </is>
       </c>
       <c r="BB117" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="BC117" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
     </row>
@@ -18222,17 +18333,17 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Hong Kong, China</t>
+          <t>France</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
@@ -18257,12 +18368,12 @@
       </c>
       <c r="L118" t="inlineStr">
         <is>
-          <t>2009-02-01</t>
+          <t>2009-01-01</t>
         </is>
       </c>
       <c r="M118" t="inlineStr">
         <is>
-          <t>2009-02</t>
+          <t>2009-01</t>
         </is>
       </c>
       <c r="N118" t="n">
@@ -18271,79 +18382,165 @@
       <c r="O118" t="n">
         <v>0</v>
       </c>
-      <c r="Q118" t="n">
-        <v>0</v>
-      </c>
-      <c r="R118" t="n">
-        <v>0</v>
-      </c>
-      <c r="S118" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+      <c r="U118" t="inlineStr">
+        <is>
+          <t>SER_FR_ECDC_ANTH_ANNUAL</t>
+        </is>
+      </c>
+      <c r="V118" t="inlineStr">
+        <is>
+          <t>SER_FR_ECDC_ANTH_ANNUAL</t>
+        </is>
+      </c>
+      <c r="W118" t="inlineStr">
+        <is>
+          <t>SRC_FR_ECDC_ATLAS</t>
+        </is>
+      </c>
+      <c r="X118" t="inlineStr">
+        <is>
+          <t>Anthrax</t>
+        </is>
+      </c>
+      <c r="Y118" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z118" t="inlineStr">
+        <is>
+          <t>ecdc_member_state_reported_aggregate_surveillance</t>
+        </is>
+      </c>
+      <c r="AA118" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="AB118" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC118" t="inlineStr">
+        <is>
+          <t>country:FR:national</t>
+        </is>
+      </c>
+      <c r="AD118" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE118" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF118" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG118" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH118" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI118" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ118" t="inlineStr">
+        <is>
+          <t>ECDC_CURRENT_GENERAL_ANNUAL_2026_08</t>
+        </is>
+      </c>
+      <c r="AK118" t="inlineStr">
+        <is>
+          <t>France annual Member-State reported aggregate cases from the public ECDC Surveillance Atlas; published zeroes are explicit, absent topic/year cells remain unknown, and combined populations are emitted only when every reviewed component is present. Data provided by ECDC based on data reported by EU/EEA Member States.</t>
+        </is>
+      </c>
+      <c r="AM118" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN118" t="b">
+        <v>1</v>
       </c>
       <c r="AO118" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP118" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR118" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS118" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ118" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS118" t="inlineStr">
+        <is>
+          <t>SER_FR_ECDC_ANTH_ANNUAL</t>
+        </is>
+      </c>
       <c r="AT118" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU118" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV118" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="AW118" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>ECDC Surveillance Atlas — France Annual Baseline</t>
         </is>
       </c>
       <c r="AX118" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="AY118" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
       <c r="AZ118" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="BA118" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>ECDC Surveillance Atlas — France Annual Baseline</t>
         </is>
       </c>
       <c r="BB118" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="BC118" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
     </row>
@@ -18375,12 +18572,12 @@
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Hong Kong, China</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
@@ -18405,18 +18602,21 @@
       </c>
       <c r="L119" t="inlineStr">
         <is>
-          <t>2009-02-01</t>
+          <t>2009-01-01</t>
         </is>
       </c>
       <c r="M119" t="inlineStr">
         <is>
-          <t>2009-02</t>
+          <t>2009-01</t>
         </is>
       </c>
       <c r="N119" t="n">
         <v>0</v>
       </c>
       <c r="O119" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q119" t="n">
         <v>0</v>
       </c>
       <c r="R119" t="n">
@@ -18453,42 +18653,42 @@
       </c>
       <c r="AV119" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="AW119" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX119" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="AY119" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ119" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="BA119" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB119" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="BC119" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -18520,12 +18720,12 @@
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>IS</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Iceland</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
@@ -18550,12 +18750,12 @@
       </c>
       <c r="L120" t="inlineStr">
         <is>
-          <t>2009-03-01</t>
+          <t>2009-01-01</t>
         </is>
       </c>
       <c r="M120" t="inlineStr">
         <is>
-          <t>2009-03</t>
+          <t>2009-01</t>
         </is>
       </c>
       <c r="N120" t="n">
@@ -18564,9 +18764,6 @@
       <c r="O120" t="n">
         <v>0</v>
       </c>
-      <c r="Q120" t="n">
-        <v>0</v>
-      </c>
       <c r="R120" t="n">
         <v>0</v>
       </c>
@@ -18575,43 +18772,57 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U120" t="inlineStr">
+        <is>
+          <t>SER_IS_HISTORY_ANTHRAX_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AA120" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
       <c r="AO120" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP120" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR120" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS120" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ120" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS120" t="inlineStr">
+        <is>
+          <t>SER_IS_HISTORY_ANTHRAX_ANNUAL</t>
+        </is>
+      </c>
       <c r="AT120" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU120" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV120" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>is_doh_annual</t>
         </is>
       </c>
       <c r="AW120" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Iceland Directorate of Health Annual Dashboard</t>
         </is>
       </c>
       <c r="AX120" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://island.is/en/smitsjukdomar-tolur</t>
         </is>
       </c>
       <c r="AY120" t="inlineStr">
@@ -18621,22 +18832,22 @@
       </c>
       <c r="AZ120" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
         </is>
       </c>
       <c r="BA120" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
         </is>
       </c>
       <c r="BB120" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
         </is>
       </c>
       <c r="BC120" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
         </is>
       </c>
     </row>
@@ -18663,17 +18874,17 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>IS</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Hong Kong, China</t>
+          <t>Iceland</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
@@ -18698,12 +18909,12 @@
       </c>
       <c r="L121" t="inlineStr">
         <is>
-          <t>2009-03-01</t>
+          <t>2009-01-01</t>
         </is>
       </c>
       <c r="M121" t="inlineStr">
         <is>
-          <t>2009-03</t>
+          <t>2009-01</t>
         </is>
       </c>
       <c r="N121" t="n">
@@ -18712,79 +18923,165 @@
       <c r="O121" t="n">
         <v>0</v>
       </c>
-      <c r="Q121" t="n">
-        <v>0</v>
-      </c>
-      <c r="R121" t="n">
-        <v>0</v>
-      </c>
-      <c r="S121" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+      <c r="U121" t="inlineStr">
+        <is>
+          <t>SER_IS_HISTORY_ANTHRAX_ANNUAL</t>
+        </is>
+      </c>
+      <c r="V121" t="inlineStr">
+        <is>
+          <t>SER_IS_HISTORY_ANTHRAX_ANNUAL</t>
+        </is>
+      </c>
+      <c r="W121" t="inlineStr">
+        <is>
+          <t>SRC_IS_DOH_HISTORY</t>
+        </is>
+      </c>
+      <c r="X121" t="inlineStr">
+        <is>
+          <t>Miltisbrandur</t>
+        </is>
+      </c>
+      <c r="Y121" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z121" t="inlineStr">
+        <is>
+          <t>national_registry_notifications</t>
+        </is>
+      </c>
+      <c r="AA121" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="AB121" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC121" t="inlineStr">
+        <is>
+          <t>country:IS:national</t>
+        </is>
+      </c>
+      <c r="AD121" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE121" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF121" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG121" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH121" t="inlineStr">
+        <is>
+          <t>historical</t>
+        </is>
+      </c>
+      <c r="AI121" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ121" t="inlineStr">
+        <is>
+          <t>IS_DOH_historical_registry_annual</t>
+        </is>
+      </c>
+      <c r="AK121" t="inlineStr">
+        <is>
+          <t>Iceland historical national-registry annual notifications; published dashes mean not applicable and blank cells remain unknown.</t>
+        </is>
+      </c>
+      <c r="AM121" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN121" t="b">
+        <v>1</v>
       </c>
       <c r="AO121" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP121" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR121" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS121" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ121" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS121" t="inlineStr">
+        <is>
+          <t>SER_IS_HISTORY_ANTHRAX_ANNUAL</t>
+        </is>
+      </c>
       <c r="AT121" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU121" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV121" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>is_doh_annual</t>
         </is>
       </c>
       <c r="AW121" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Iceland Directorate of Health Annual Dashboard</t>
         </is>
       </c>
       <c r="AX121" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://island.is/en/smitsjukdomar-tolur</t>
         </is>
       </c>
       <c r="AY121" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ121" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
         </is>
       </c>
       <c r="BA121" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
         </is>
       </c>
       <c r="BB121" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
         </is>
       </c>
       <c r="BC121" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
         </is>
       </c>
     </row>
@@ -18846,12 +19143,12 @@
       </c>
       <c r="L122" t="inlineStr">
         <is>
-          <t>2009-03-01</t>
+          <t>2009-01-01</t>
         </is>
       </c>
       <c r="M122" t="inlineStr">
         <is>
-          <t>2009-03</t>
+          <t>2009-01</t>
         </is>
       </c>
       <c r="N122" t="n">
@@ -18991,12 +19288,12 @@
       </c>
       <c r="L123" t="inlineStr">
         <is>
-          <t>2009-04-01</t>
+          <t>2009-02-01</t>
         </is>
       </c>
       <c r="M123" t="inlineStr">
         <is>
-          <t>2009-04</t>
+          <t>2009-02</t>
         </is>
       </c>
       <c r="N123" t="n">
@@ -19139,12 +19436,12 @@
       </c>
       <c r="L124" t="inlineStr">
         <is>
-          <t>2009-04-01</t>
+          <t>2009-02-01</t>
         </is>
       </c>
       <c r="M124" t="inlineStr">
         <is>
-          <t>2009-04</t>
+          <t>2009-02</t>
         </is>
       </c>
       <c r="N124" t="n">
@@ -19287,12 +19584,12 @@
       </c>
       <c r="L125" t="inlineStr">
         <is>
-          <t>2009-04-01</t>
+          <t>2009-02-01</t>
         </is>
       </c>
       <c r="M125" t="inlineStr">
         <is>
-          <t>2009-04</t>
+          <t>2009-02</t>
         </is>
       </c>
       <c r="N125" t="n">
@@ -19432,12 +19729,12 @@
       </c>
       <c r="L126" t="inlineStr">
         <is>
-          <t>2009-05-01</t>
+          <t>2009-03-01</t>
         </is>
       </c>
       <c r="M126" t="inlineStr">
         <is>
-          <t>2009-05</t>
+          <t>2009-03</t>
         </is>
       </c>
       <c r="N126" t="n">
@@ -19580,12 +19877,12 @@
       </c>
       <c r="L127" t="inlineStr">
         <is>
-          <t>2009-05-01</t>
+          <t>2009-03-01</t>
         </is>
       </c>
       <c r="M127" t="inlineStr">
         <is>
-          <t>2009-05</t>
+          <t>2009-03</t>
         </is>
       </c>
       <c r="N127" t="n">
@@ -19728,12 +20025,12 @@
       </c>
       <c r="L128" t="inlineStr">
         <is>
-          <t>2009-05-01</t>
+          <t>2009-03-01</t>
         </is>
       </c>
       <c r="M128" t="inlineStr">
         <is>
-          <t>2009-05</t>
+          <t>2009-03</t>
         </is>
       </c>
       <c r="N128" t="n">
@@ -19873,12 +20170,12 @@
       </c>
       <c r="L129" t="inlineStr">
         <is>
-          <t>2009-06-01</t>
+          <t>2009-04-01</t>
         </is>
       </c>
       <c r="M129" t="inlineStr">
         <is>
-          <t>2009-06</t>
+          <t>2009-04</t>
         </is>
       </c>
       <c r="N129" t="n">
@@ -20021,12 +20318,12 @@
       </c>
       <c r="L130" t="inlineStr">
         <is>
-          <t>2009-06-01</t>
+          <t>2009-04-01</t>
         </is>
       </c>
       <c r="M130" t="inlineStr">
         <is>
-          <t>2009-06</t>
+          <t>2009-04</t>
         </is>
       </c>
       <c r="N130" t="n">
@@ -20169,12 +20466,12 @@
       </c>
       <c r="L131" t="inlineStr">
         <is>
-          <t>2009-06-01</t>
+          <t>2009-04-01</t>
         </is>
       </c>
       <c r="M131" t="inlineStr">
         <is>
-          <t>2009-06</t>
+          <t>2009-04</t>
         </is>
       </c>
       <c r="N131" t="n">
@@ -20314,12 +20611,12 @@
       </c>
       <c r="L132" t="inlineStr">
         <is>
-          <t>2009-07-01</t>
+          <t>2009-05-01</t>
         </is>
       </c>
       <c r="M132" t="inlineStr">
         <is>
-          <t>2009-07</t>
+          <t>2009-05</t>
         </is>
       </c>
       <c r="N132" t="n">
@@ -20462,12 +20759,12 @@
       </c>
       <c r="L133" t="inlineStr">
         <is>
-          <t>2009-07-01</t>
+          <t>2009-05-01</t>
         </is>
       </c>
       <c r="M133" t="inlineStr">
         <is>
-          <t>2009-07</t>
+          <t>2009-05</t>
         </is>
       </c>
       <c r="N133" t="n">
@@ -20610,12 +20907,12 @@
       </c>
       <c r="L134" t="inlineStr">
         <is>
-          <t>2009-07-01</t>
+          <t>2009-05-01</t>
         </is>
       </c>
       <c r="M134" t="inlineStr">
         <is>
-          <t>2009-07</t>
+          <t>2009-05</t>
         </is>
       </c>
       <c r="N134" t="n">
@@ -20755,12 +21052,12 @@
       </c>
       <c r="L135" t="inlineStr">
         <is>
-          <t>2009-08-01</t>
+          <t>2009-06-01</t>
         </is>
       </c>
       <c r="M135" t="inlineStr">
         <is>
-          <t>2009-08</t>
+          <t>2009-06</t>
         </is>
       </c>
       <c r="N135" t="n">
@@ -20903,12 +21200,12 @@
       </c>
       <c r="L136" t="inlineStr">
         <is>
-          <t>2009-08-01</t>
+          <t>2009-06-01</t>
         </is>
       </c>
       <c r="M136" t="inlineStr">
         <is>
-          <t>2009-08</t>
+          <t>2009-06</t>
         </is>
       </c>
       <c r="N136" t="n">
@@ -21051,12 +21348,12 @@
       </c>
       <c r="L137" t="inlineStr">
         <is>
-          <t>2009-08-01</t>
+          <t>2009-06-01</t>
         </is>
       </c>
       <c r="M137" t="inlineStr">
         <is>
-          <t>2009-08</t>
+          <t>2009-06</t>
         </is>
       </c>
       <c r="N137" t="n">
@@ -21196,12 +21493,12 @@
       </c>
       <c r="L138" t="inlineStr">
         <is>
-          <t>2009-09-01</t>
+          <t>2009-07-01</t>
         </is>
       </c>
       <c r="M138" t="inlineStr">
         <is>
-          <t>2009-09</t>
+          <t>2009-07</t>
         </is>
       </c>
       <c r="N138" t="n">
@@ -21344,12 +21641,12 @@
       </c>
       <c r="L139" t="inlineStr">
         <is>
-          <t>2009-09-01</t>
+          <t>2009-07-01</t>
         </is>
       </c>
       <c r="M139" t="inlineStr">
         <is>
-          <t>2009-09</t>
+          <t>2009-07</t>
         </is>
       </c>
       <c r="N139" t="n">
@@ -21492,12 +21789,12 @@
       </c>
       <c r="L140" t="inlineStr">
         <is>
-          <t>2009-09-01</t>
+          <t>2009-07-01</t>
         </is>
       </c>
       <c r="M140" t="inlineStr">
         <is>
-          <t>2009-09</t>
+          <t>2009-07</t>
         </is>
       </c>
       <c r="N140" t="n">
@@ -21637,12 +21934,12 @@
       </c>
       <c r="L141" t="inlineStr">
         <is>
-          <t>2009-10-01</t>
+          <t>2009-08-01</t>
         </is>
       </c>
       <c r="M141" t="inlineStr">
         <is>
-          <t>2009-10</t>
+          <t>2009-08</t>
         </is>
       </c>
       <c r="N141" t="n">
@@ -21785,12 +22082,12 @@
       </c>
       <c r="L142" t="inlineStr">
         <is>
-          <t>2009-10-01</t>
+          <t>2009-08-01</t>
         </is>
       </c>
       <c r="M142" t="inlineStr">
         <is>
-          <t>2009-10</t>
+          <t>2009-08</t>
         </is>
       </c>
       <c r="N142" t="n">
@@ -21933,12 +22230,12 @@
       </c>
       <c r="L143" t="inlineStr">
         <is>
-          <t>2009-10-01</t>
+          <t>2009-08-01</t>
         </is>
       </c>
       <c r="M143" t="inlineStr">
         <is>
-          <t>2009-10</t>
+          <t>2009-08</t>
         </is>
       </c>
       <c r="N143" t="n">
@@ -22078,12 +22375,12 @@
       </c>
       <c r="L144" t="inlineStr">
         <is>
-          <t>2009-11-01</t>
+          <t>2009-09-01</t>
         </is>
       </c>
       <c r="M144" t="inlineStr">
         <is>
-          <t>2009-11</t>
+          <t>2009-09</t>
         </is>
       </c>
       <c r="N144" t="n">
@@ -22226,12 +22523,12 @@
       </c>
       <c r="L145" t="inlineStr">
         <is>
-          <t>2009-11-01</t>
+          <t>2009-09-01</t>
         </is>
       </c>
       <c r="M145" t="inlineStr">
         <is>
-          <t>2009-11</t>
+          <t>2009-09</t>
         </is>
       </c>
       <c r="N145" t="n">
@@ -22374,12 +22671,12 @@
       </c>
       <c r="L146" t="inlineStr">
         <is>
-          <t>2009-11-01</t>
+          <t>2009-09-01</t>
         </is>
       </c>
       <c r="M146" t="inlineStr">
         <is>
-          <t>2009-11</t>
+          <t>2009-09</t>
         </is>
       </c>
       <c r="N146" t="n">
@@ -22519,12 +22816,12 @@
       </c>
       <c r="L147" t="inlineStr">
         <is>
-          <t>2009-12-01</t>
+          <t>2009-10-01</t>
         </is>
       </c>
       <c r="M147" t="inlineStr">
         <is>
-          <t>2009-12</t>
+          <t>2009-10</t>
         </is>
       </c>
       <c r="N147" t="n">
@@ -22667,12 +22964,12 @@
       </c>
       <c r="L148" t="inlineStr">
         <is>
-          <t>2009-12-01</t>
+          <t>2009-10-01</t>
         </is>
       </c>
       <c r="M148" t="inlineStr">
         <is>
-          <t>2009-12</t>
+          <t>2009-10</t>
         </is>
       </c>
       <c r="N148" t="n">
@@ -22815,12 +23112,12 @@
       </c>
       <c r="L149" t="inlineStr">
         <is>
-          <t>2009-12-01</t>
+          <t>2009-10-01</t>
         </is>
       </c>
       <c r="M149" t="inlineStr">
         <is>
-          <t>2009-12</t>
+          <t>2009-10</t>
         </is>
       </c>
       <c r="N149" t="n">
@@ -22897,6 +23194,888 @@
         </is>
       </c>
       <c r="BC149" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>D023</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>anthrax</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>Anthrax</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>AU</t>
+        </is>
+      </c>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>D023</t>
+        </is>
+      </c>
+      <c r="I150" t="inlineStr">
+        <is>
+          <t>Anthrax</t>
+        </is>
+      </c>
+      <c r="J150" t="inlineStr">
+        <is>
+          <t>炭疽</t>
+        </is>
+      </c>
+      <c r="K150" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L150" t="inlineStr">
+        <is>
+          <t>2009-11-01</t>
+        </is>
+      </c>
+      <c r="M150" t="inlineStr">
+        <is>
+          <t>2009-11</t>
+        </is>
+      </c>
+      <c r="N150" t="n">
+        <v>0</v>
+      </c>
+      <c r="O150" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q150" t="n">
+        <v>0</v>
+      </c>
+      <c r="R150" t="n">
+        <v>0</v>
+      </c>
+      <c r="S150" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO150" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP150" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR150" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS150" t="inlineStr"/>
+      <c r="AT150" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU150" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV150" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW150" t="inlineStr">
+        <is>
+          <t>Australia NINDSS</t>
+        </is>
+      </c>
+      <c r="AX150" t="inlineStr">
+        <is>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+        </is>
+      </c>
+      <c r="AY150" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ150" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA150" t="inlineStr">
+        <is>
+          <t>Australia NINDSS</t>
+        </is>
+      </c>
+      <c r="BB150" t="inlineStr">
+        <is>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+        </is>
+      </c>
+      <c r="BC150" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>D023</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>anthrax</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>Anthrax</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>HK</t>
+        </is>
+      </c>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>Hong Kong, China</t>
+        </is>
+      </c>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>D023</t>
+        </is>
+      </c>
+      <c r="I151" t="inlineStr">
+        <is>
+          <t>Anthrax</t>
+        </is>
+      </c>
+      <c r="J151" t="inlineStr">
+        <is>
+          <t>炭疽</t>
+        </is>
+      </c>
+      <c r="K151" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L151" t="inlineStr">
+        <is>
+          <t>2009-11-01</t>
+        </is>
+      </c>
+      <c r="M151" t="inlineStr">
+        <is>
+          <t>2009-11</t>
+        </is>
+      </c>
+      <c r="N151" t="n">
+        <v>0</v>
+      </c>
+      <c r="O151" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q151" t="n">
+        <v>0</v>
+      </c>
+      <c r="R151" t="n">
+        <v>0</v>
+      </c>
+      <c r="S151" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO151" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP151" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR151" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS151" t="inlineStr"/>
+      <c r="AT151" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU151" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV151" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="AW151" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="AX151" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="AY151" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+      <c r="AZ151" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="BA151" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="BB151" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="BC151" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>D023</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>anthrax</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>Anthrax</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>KR</t>
+        </is>
+      </c>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>South Korea</t>
+        </is>
+      </c>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>D023</t>
+        </is>
+      </c>
+      <c r="I152" t="inlineStr">
+        <is>
+          <t>Anthrax</t>
+        </is>
+      </c>
+      <c r="J152" t="inlineStr">
+        <is>
+          <t>炭疽</t>
+        </is>
+      </c>
+      <c r="K152" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L152" t="inlineStr">
+        <is>
+          <t>2009-11-01</t>
+        </is>
+      </c>
+      <c r="M152" t="inlineStr">
+        <is>
+          <t>2009-11</t>
+        </is>
+      </c>
+      <c r="N152" t="n">
+        <v>0</v>
+      </c>
+      <c r="O152" t="n">
+        <v>0</v>
+      </c>
+      <c r="R152" t="n">
+        <v>0</v>
+      </c>
+      <c r="S152" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO152" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP152" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR152" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS152" t="inlineStr"/>
+      <c r="AT152" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU152" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV152" t="inlineStr">
+        <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="AW152" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="AX152" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="AY152" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
+        </is>
+      </c>
+      <c r="AZ152" t="inlineStr">
+        <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="BA152" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="BB152" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="BC152" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>D023</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>anthrax</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>Anthrax</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>AU</t>
+        </is>
+      </c>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="H153" t="inlineStr">
+        <is>
+          <t>D023</t>
+        </is>
+      </c>
+      <c r="I153" t="inlineStr">
+        <is>
+          <t>Anthrax</t>
+        </is>
+      </c>
+      <c r="J153" t="inlineStr">
+        <is>
+          <t>炭疽</t>
+        </is>
+      </c>
+      <c r="K153" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L153" t="inlineStr">
+        <is>
+          <t>2009-12-01</t>
+        </is>
+      </c>
+      <c r="M153" t="inlineStr">
+        <is>
+          <t>2009-12</t>
+        </is>
+      </c>
+      <c r="N153" t="n">
+        <v>0</v>
+      </c>
+      <c r="O153" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q153" t="n">
+        <v>0</v>
+      </c>
+      <c r="R153" t="n">
+        <v>0</v>
+      </c>
+      <c r="S153" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO153" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP153" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR153" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS153" t="inlineStr"/>
+      <c r="AT153" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU153" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV153" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW153" t="inlineStr">
+        <is>
+          <t>Australia NINDSS</t>
+        </is>
+      </c>
+      <c r="AX153" t="inlineStr">
+        <is>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+        </is>
+      </c>
+      <c r="AY153" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ153" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA153" t="inlineStr">
+        <is>
+          <t>Australia NINDSS</t>
+        </is>
+      </c>
+      <c r="BB153" t="inlineStr">
+        <is>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+        </is>
+      </c>
+      <c r="BC153" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>D023</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>anthrax</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>Anthrax</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>HK</t>
+        </is>
+      </c>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>Hong Kong, China</t>
+        </is>
+      </c>
+      <c r="H154" t="inlineStr">
+        <is>
+          <t>D023</t>
+        </is>
+      </c>
+      <c r="I154" t="inlineStr">
+        <is>
+          <t>Anthrax</t>
+        </is>
+      </c>
+      <c r="J154" t="inlineStr">
+        <is>
+          <t>炭疽</t>
+        </is>
+      </c>
+      <c r="K154" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L154" t="inlineStr">
+        <is>
+          <t>2009-12-01</t>
+        </is>
+      </c>
+      <c r="M154" t="inlineStr">
+        <is>
+          <t>2009-12</t>
+        </is>
+      </c>
+      <c r="N154" t="n">
+        <v>0</v>
+      </c>
+      <c r="O154" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q154" t="n">
+        <v>0</v>
+      </c>
+      <c r="R154" t="n">
+        <v>0</v>
+      </c>
+      <c r="S154" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO154" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP154" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR154" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS154" t="inlineStr"/>
+      <c r="AT154" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU154" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV154" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="AW154" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="AX154" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="AY154" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+      <c r="AZ154" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="BA154" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="BB154" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="BC154" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>D023</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>anthrax</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>Anthrax</t>
+        </is>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>KR</t>
+        </is>
+      </c>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>South Korea</t>
+        </is>
+      </c>
+      <c r="H155" t="inlineStr">
+        <is>
+          <t>D023</t>
+        </is>
+      </c>
+      <c r="I155" t="inlineStr">
+        <is>
+          <t>Anthrax</t>
+        </is>
+      </c>
+      <c r="J155" t="inlineStr">
+        <is>
+          <t>炭疽</t>
+        </is>
+      </c>
+      <c r="K155" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L155" t="inlineStr">
+        <is>
+          <t>2009-12-01</t>
+        </is>
+      </c>
+      <c r="M155" t="inlineStr">
+        <is>
+          <t>2009-12</t>
+        </is>
+      </c>
+      <c r="N155" t="n">
+        <v>0</v>
+      </c>
+      <c r="O155" t="n">
+        <v>0</v>
+      </c>
+      <c r="R155" t="n">
+        <v>0</v>
+      </c>
+      <c r="S155" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO155" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP155" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR155" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS155" t="inlineStr"/>
+      <c r="AT155" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU155" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV155" t="inlineStr">
+        <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="AW155" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="AX155" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="AY155" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
+        </is>
+      </c>
+      <c r="AZ155" t="inlineStr">
+        <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="BA155" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="BB155" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="BC155" t="inlineStr">
         <is>
           <t>open_api_or_portal_download</t>
         </is>
@@ -23018,7 +24197,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>143</v>
+        <v>146</v>
       </c>
     </row>
     <row r="10">
@@ -23028,7 +24207,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>148</v>
+        <v>154</v>
       </c>
     </row>
     <row r="11">
@@ -23048,7 +24227,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="13">
@@ -23058,7 +24237,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14">
